--- a/results/comparison_SimpleRAG/SimpleRAG_evaluated.xlsx
+++ b/results/comparison_SimpleRAG/SimpleRAG_evaluated.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1977186272723331</v>
+        <v>0.2097902048404433</v>
       </c>
       <c r="D2" t="n">
-        <v>0.008388953337667307</v>
+        <v>7.752069396152736e-79</v>
       </c>
       <c r="E2" t="n">
-        <v>0.604053258895874</v>
+        <v>0.5977494120597839</v>
       </c>
       <c r="F2" t="n">
-        <v>37.89255681818184</v>
+        <v>22.91078296703299</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3907284768211921</v>
+        <v>1.216650898770104</v>
       </c>
       <c r="H2" t="n">
         <v>0.6</v>
@@ -527,7 +527,2641 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
+        <v>0.3055555555555556</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.04999999882812503</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.43487389729896e-232</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.4237347543239594</v>
+      </c>
+      <c r="F3" t="n">
+        <v>40.57862068965517</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8.045871559633028</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.2207792207792208</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.2024539827392828</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.236532508081141e-79</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.5616869926452637</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6.75472103004293</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9604700854700855</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.173333329330889</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.771288619043119e-156</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.5040472745895386</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.103526315789509</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3788870703764321</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.2390438199241283</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.387998585949857e-79</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.4997581243515015</v>
+      </c>
+      <c r="F6" t="n">
+        <v>19.98151356080493</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5816091954022988</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.135593217546165</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.529719427055785e-82</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.5666908621788025</v>
+      </c>
+      <c r="F7" t="n">
+        <v>51.32778017241381</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1635146930462613</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.1752577319587629</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.1824104196305532</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.876089683198407e-157</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.550324022769928</v>
+      </c>
+      <c r="F8" t="n">
+        <v>60.09759615384617</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2909722222222222</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.08163265306122448</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1477162253787302</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.782460578498421e-79</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.4941553473472595</v>
+      </c>
+      <c r="F9" t="n">
+        <v>33.9719155773814</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.805909617612978</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.6396396396396395</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.02429149734891575</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.576672074727729e-258</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.3601222634315491</v>
+      </c>
+      <c r="F10" t="n">
+        <v>54.72500000000002</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.05489417989417989</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.03225806336545269</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.055947193323949e-248</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.3789161145687103</v>
+      </c>
+      <c r="F11" t="n">
+        <v>15.40352941176474</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.08091853471842538</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1071428571428571</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.1349527618234834</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.006197991977315e-155</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.5133850574493408</v>
+      </c>
+      <c r="F12" t="n">
+        <v>29.40905921767478</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.390660592255125</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2125984251968504</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.006622516166834812</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.563850370796146e-306</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3030001223087311</v>
+      </c>
+      <c r="F13" t="n">
+        <v>78.58166666666669</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.03880266075388027</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.1238938004141978</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.831582307030143e-155</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.4769697785377502</v>
+      </c>
+      <c r="F14" t="n">
+        <v>38.07181512301014</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2592592592592592</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.1034482709737088</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8.336198329589075e-232</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.4232414960861206</v>
+      </c>
+      <c r="F15" t="n">
+        <v>32.47375000000002</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8309859154929577</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.1379310344827586</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.09210525910058882</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.931385032645776e-155</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.4577217102050781</v>
+      </c>
+      <c r="F16" t="n">
+        <v>38.94837147729316</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.708987161198288</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.3233082706766917</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.08979591437526049</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.004927453015568e-155</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.4553513526916504</v>
+      </c>
+      <c r="F17" t="n">
+        <v>24.69052445961319</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.71505376344086</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.2982456140350877</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.1221995895721356</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.046592697329324e-157</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.4743372797966003</v>
+      </c>
+      <c r="F18" t="n">
+        <v>49.76303278688528</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.2102803738317757</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.2156862745098039</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.1324999957507814</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.376584323444934e-155</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.4687531590461731</v>
+      </c>
+      <c r="F19" t="n">
+        <v>34.84329544101894</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.141727092946605</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.393939393939394</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.1160409528460437</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.511461192573111e-158</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.4007299840450287</v>
+      </c>
+      <c r="F20" t="n">
+        <v>34.02192307692312</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.1923349893541519</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.1524390210328674</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5.344813770404013e-158</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.44349405169487</v>
+      </c>
+      <c r="F21" t="n">
+        <v>38.45019230769233</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.2084985835694051</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.02313624678663239</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.04379561914726414</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3.956540474391853e-167</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.4157088994979858</v>
+      </c>
+      <c r="F22" t="n">
+        <v>58.42368421052632</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.08969696969696969</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.04347826086956522</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.1282051234350771</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3.740453798441815e-155</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.4942657947540283</v>
+      </c>
+      <c r="F23" t="n">
+        <v>40.94661303462323</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.418465778594396</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.5862068965517241</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.01834862297786386</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5.70549465579852e-248</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.2839576303958893</v>
+      </c>
+      <c r="F24" t="n">
+        <v>100.24</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.1059907834101382</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.1032258025007286</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.86440460314551e-233</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.383302628993988</v>
+      </c>
+      <c r="F25" t="n">
+        <v>54.37000000000003</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.3529411764705883</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.1428571384948981</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.016828805938773e-232</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.4139982759952545</v>
+      </c>
+      <c r="F26" t="n">
+        <v>62.09000000000003</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.4714038128249567</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.05681817780023272</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4.116874532089826e-233</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.4149340093135834</v>
+      </c>
+      <c r="F27" t="n">
+        <v>39.59916666666669</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.3885088919288646</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.06212121212121212</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.03448275565546994</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4.107503120299131e-235</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.3858523368835449</v>
+      </c>
+      <c r="F29" t="n">
+        <v>66.42336956521743</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.2760416666666667</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.03174602929705234</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6.344261789253943e-232</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.4453355371952057</v>
+      </c>
+      <c r="F30" t="n">
+        <v>17.09264084507043</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.1919191919191919</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.3297283351421356</v>
+      </c>
+      <c r="F31" t="n">
+        <v>120.205</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.4563106796116505</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.431653618812561</v>
+      </c>
+      <c r="F32" t="n">
+        <v>25.79500000000004</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.0625</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.1052631536738229</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.225701556969266e-232</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.4636627733707428</v>
+      </c>
+      <c r="F33" t="n">
+        <v>68.77000000000002</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.4404432132963989</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.3589319586753845</v>
+      </c>
+      <c r="F34" t="n">
+        <v>78.92000000000003</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.07848837209302326</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.09427608985432347</v>
+      </c>
+      <c r="D35" t="n">
+        <v>5.537127353092394e-156</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.4941136240959167</v>
+      </c>
+      <c r="F35" t="n">
+        <v>48.5257843137255</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.5542907180385289</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.1970802919708029</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.09999999503347133</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2.373266882338666e-155</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.4774568676948547</v>
+      </c>
+      <c r="F36" t="n">
+        <v>32.15861971830986</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.10459587955626</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.2592592592592592</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.2126203328371048</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.04453870625662779</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.3307868242263794</v>
+      </c>
+      <c r="F38" t="n">
+        <v>34.59000000000003</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.07632600258732213</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.01612903025494301</v>
+      </c>
+      <c r="D39" t="n">
+        <v>6.70210840219247e-236</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.4022384285926819</v>
+      </c>
+      <c r="F39" t="n">
+        <v>24.52980769230771</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.1946902654867257</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.01183431790903702</v>
+      </c>
+      <c r="D40" t="n">
+        <v>4.705259671664536e-241</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.3769575953483582</v>
+      </c>
+      <c r="F40" t="n">
+        <v>30.33294117647063</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.1596916299559471</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.08108107864590949</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4.552834747218141e-160</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.3969779014587402</v>
+      </c>
+      <c r="F41" t="n">
+        <v>18.73000000000002</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.1803840877914952</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.09248554699989982</v>
+      </c>
+      <c r="D42" t="n">
+        <v>9.223014754463368e-237</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.3830304741859436</v>
+      </c>
+      <c r="F42" t="n">
+        <v>91.84272727272729</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.1737142857142857</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.01142857087346942</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3.147472882101898e-250</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.3573367297649384</v>
+      </c>
+      <c r="F43" t="n">
+        <v>73.84500000000001</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.07136237256719184</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.02222222222222222</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.04707233065442021</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.03007518731612868</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1.736541508818539e-187</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.4082158803939819</v>
+      </c>
+      <c r="F45" t="n">
+        <v>51.17500000000004</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.03948450781464217</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.02846975033649524</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2.473429082801671e-186</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.3992475271224976</v>
+      </c>
+      <c r="F46" t="n">
+        <v>63.86500000000004</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.03849349210744946</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.06976743976971343</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1.47796399693611e-161</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.4906946420669556</v>
+      </c>
+      <c r="F47" t="n">
+        <v>57.68987500000003</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.1355121562375448</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.08080807607795151</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.08166174686698e-231</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.4793923795223236</v>
+      </c>
+      <c r="F48" t="n">
+        <v>47.1128967642527</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1.646680942184154</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.3233082706766917</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.04040403842873186</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3.225165604459343e-237</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.3527005910873413</v>
+      </c>
+      <c r="F49" t="n">
+        <v>47.30000000000004</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.1811175337186898</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.4269594848155975</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-53.65230769230766</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.3026819923371648</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.06976744186046512</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.1333333295382921</v>
+      </c>
+      <c r="D51" t="n">
+        <v>5.207709068344895e-233</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.453571230173111</v>
+      </c>
+      <c r="F51" t="n">
+        <v>60.42338435374151</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.3635153129161118</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.07894736842105263</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.1134328315854758</v>
+      </c>
+      <c r="D52" t="n">
+        <v>5.426938259447703e-156</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.4633342623710632</v>
+      </c>
+      <c r="F52" t="n">
+        <v>35.83857014388494</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.4234952864394489</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L52" t="n">
         <v>0.2307692307692308</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.1400966141808445</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2.288954924777743e-156</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.4370111227035522</v>
+      </c>
+      <c r="F53" t="n">
+        <v>53.05714285714291</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.3511205976520811</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.1724137931034483</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.09774435749222693</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.499344503805113e-234</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.4339385032653809</v>
+      </c>
+      <c r="F54" t="n">
+        <v>47.02438380281694</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.2781456953642384</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.03265306044148274</v>
+      </c>
+      <c r="D55" t="n">
+        <v>6.926795000328894e-256</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.3838652968406677</v>
+      </c>
+      <c r="F55" t="n">
+        <v>25.45500000000001</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.0795601552393273</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.04395604229226214</v>
+      </c>
+      <c r="D56" t="n">
+        <v>3.389640397060023e-241</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.3971304297447205</v>
+      </c>
+      <c r="F56" t="n">
+        <v>68.74642857142858</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.1142310146777281</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.00877192956486612</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3.987454504377973e-305</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.3450036346912384</v>
+      </c>
+      <c r="F57" t="n">
+        <v>54.70142857142861</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.02929014472777395</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.04427645788336933</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.01492537227890404</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.276363192714411e-249</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.3753083646297455</v>
+      </c>
+      <c r="F59" t="n">
+        <v>64.3125</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.1060606060606061</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.02643171758883348</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.208538305956385e-268</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.3580284416675568</v>
+      </c>
+      <c r="F60" t="n">
+        <v>80.30636363636367</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.0363382250174703</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.05357142473373752</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2.112416088207527e-155</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.4592677354812622</v>
+      </c>
+      <c r="F61" t="n">
+        <v>35.27727591036415</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2.340080971659919</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.2592592592592592</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.03669724328255251</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.188848263190301e-232</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.4471244513988495</v>
+      </c>
+      <c r="F62" t="n">
+        <v>60.27721153846156</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.1290322539894787</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2.774255993626391e-156</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.4963289499282837</v>
+      </c>
+      <c r="F63" t="n">
+        <v>54.16250000000002</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.5188284518828452</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.1509433962264151</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.09090908813131321</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.047507443769133e-234</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.4143487513065338</v>
+      </c>
+      <c r="F64" t="n">
+        <v>52.86800000000002</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.2737704918032787</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.07999999502759214</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.433547212720887e-155</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.4473456144332886</v>
+      </c>
+      <c r="F65" t="n">
+        <v>36.1379049844237</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1.06813627254509</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.256198347107438</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.05617977247822258</v>
+      </c>
+      <c r="D66" t="n">
+        <v>8.847183629485189e-235</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.455511212348938</v>
+      </c>
+      <c r="F66" t="n">
+        <v>33.59637254901963</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.2948557089084065</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.0536912727462728</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.948489674239513e-235</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.4413567781448364</v>
+      </c>
+      <c r="F67" t="n">
+        <v>32.505</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.2575342465753425</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SimpleRAG</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.07812499793090825</v>
+      </c>
+      <c r="D68" t="n">
+        <v>8.259885936748448e-232</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.401381641626358</v>
+      </c>
+      <c r="F68" t="n">
+        <v>34.42500000000004</v>
+      </c>
+      <c r="G68" t="n">
+        <v>4.811023622047244</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.4871794871794872</v>
       </c>
     </row>
   </sheetData>
